--- a/Results/lica_placebo_nEXTERNAL_VALIDATION_SUMMARY.xlsx
+++ b/Results/lica_placebo_nEXTERNAL_VALIDATION_SUMMARY.xlsx
@@ -456,7 +456,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -472,7 +472,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Age, Onset_Limb, Sex_Male, Diagnostic_Delay, Age_sq</t>
+          <t>Age, Onset_Limb, Sex_Male, Diagnostic_Delay, Age_Sex</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -488,7 +488,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>0.654</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -504,12 +504,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>0.664</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[0.649, 0.737]</t>
+          <t>[0.627, 0.695]</t>
         </is>
       </c>
     </row>
@@ -524,12 +524,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>0.562</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[0.885, 1.659]</t>
+          <t>[0.422, 0.741]</t>
         </is>
       </c>
     </row>
@@ -539,17 +539,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Observed KM risk at 20 months</t>
+          <t>Observed KM risk at 25 months</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.290</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[0.224, 0.347]</t>
+          <t>[0.353, 0.464]</t>
         </is>
       </c>
     </row>
@@ -559,17 +559,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mean predicted risk at 20 months (frozen)</t>
+          <t>Mean predicted risk at 25 months (frozen)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>0.203</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[0.438, 0.514]</t>
+          <t>[0.182, 0.218]</t>
         </is>
       </c>
     </row>
@@ -579,17 +579,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CITL at 20 months (frozen)</t>
+          <t>CITL at 25 months (frozen)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.225</t>
+          <t>1.203</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[-1.256, -0.402]</t>
+          <t>[0.817, 1.253]</t>
         </is>
       </c>
     </row>
@@ -604,12 +604,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>2.375</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[0.364, 0.729]</t>
+          <t>[2.018, 2.845]</t>
         </is>
       </c>
     </row>
@@ -619,17 +619,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mean predicted risk at 20 months (baseline-updated)</t>
+          <t>Mean predicted risk at 25 months (baseline-updated)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>0.345</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[0.267, 0.374]</t>
+          <t>[0.309, 0.372]</t>
         </is>
       </c>
     </row>
@@ -639,17 +639,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CITL at 20 months (baseline-updated)</t>
+          <t>CITL at 25 months (baseline-updated)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.263</t>
+          <t>0.136</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[-0.242, -0.090]</t>
+          <t>[0.201, 0.380]</t>
         </is>
       </c>
     </row>
